--- a/src/main/resources/excel-template/车辆记录.xlsx
+++ b/src/main/resources/excel-template/车辆记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\parking-system-github\parking-system-github\parking\backend\src\main\resources\excel-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA4EE22-9F70-4B83-8CEF-ABFC2A08B33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A225564-ABD6-4E56-919B-E0FFCAAF7096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>车牌号</t>
   </si>
@@ -55,9 +55,6 @@
     <t>川A12345</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>EXITED</t>
   </si>
   <si>
@@ -70,13 +67,18 @@
     <t>A009</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>PARKING</t>
   </si>
   <si>
     <t>A001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>川D87345</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A008</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -472,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="20" customWidth="1"/>
@@ -515,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2">
         <v>46220.739699074074</v>
@@ -523,11 +525,11 @@
       <c r="E2" s="2">
         <v>46221.398865740739</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
       </c>
       <c r="H2" s="2">
         <v>46222.469637766204</v>
@@ -538,27 +540,53 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
       </c>
       <c r="D3" s="2">
         <v>46222.469872685186</v>
       </c>
-      <c r="F3" t="s">
-        <v>16</v>
+      <c r="F3" t="b">
+        <v>1</v>
       </c>
       <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2">
+        <v>46222.469872685186</v>
+      </c>
+      <c r="I3" s="2">
+        <v>46222.469872928239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="2">
-        <v>46222.469872928239</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46222.469872685186</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2">
+        <v>46222.469872685186</v>
+      </c>
+      <c r="I4" s="2">
         <v>46222.469872928239</v>
       </c>
     </row>
